--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.76412</v>
+        <v>16.70542</v>
       </c>
       <c r="D2" t="n">
-        <v>16.75026</v>
+        <v>16.12202</v>
       </c>
       <c r="E2" t="n">
-        <v>16.71712</v>
+        <v>16.45034</v>
       </c>
       <c r="F2" t="n">
-        <v>42.1831</v>
+        <v>42.60457</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05073</v>
+        <v>0.05042</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80852</v>
+        <v>1.80692</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.51472</v>
+        <v>16.88556</v>
       </c>
       <c r="D3" t="n">
-        <v>16.47964</v>
+        <v>16.35295</v>
       </c>
       <c r="E3" t="n">
-        <v>16.93687</v>
+        <v>16.75805</v>
       </c>
       <c r="F3" t="n">
-        <v>41.8453</v>
+        <v>42.76316</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05058</v>
+        <v>0.05075</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83327</v>
+        <v>1.85324</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.80456</v>
+        <v>16.92675</v>
       </c>
       <c r="D4" t="n">
-        <v>16.78649</v>
+        <v>16.73958</v>
       </c>
       <c r="E4" t="n">
-        <v>16.77943</v>
+        <v>16.79872</v>
       </c>
       <c r="F4" t="n">
-        <v>42.56267</v>
+        <v>42.23453</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05013</v>
+        <v>0.05021</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85687</v>
+        <v>1.83998</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.68822</v>
+        <v>16.86037</v>
       </c>
       <c r="D6" t="n">
-        <v>15.85676</v>
+        <v>15.84064</v>
       </c>
       <c r="E6" t="n">
-        <v>16.38377</v>
+        <v>16.47372</v>
       </c>
       <c r="F6" t="n">
-        <v>21.65915</v>
+        <v>21.74867</v>
       </c>
       <c r="G6" t="n">
-        <v>33.88934</v>
+        <v>34.82133</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.80307</v>
+        <v>16.85128</v>
       </c>
       <c r="D7" t="n">
-        <v>15.8751</v>
+        <v>15.80716</v>
       </c>
       <c r="E7" t="n">
-        <v>15.95795</v>
+        <v>16.09512</v>
       </c>
       <c r="F7" t="n">
-        <v>22.15511</v>
+        <v>21.83171</v>
       </c>
       <c r="G7" t="n">
-        <v>34.7181</v>
+        <v>33.75842</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.71667</v>
+        <v>16.74952</v>
       </c>
       <c r="D8" t="n">
-        <v>15.98677</v>
+        <v>16.09657</v>
       </c>
       <c r="E8" t="n">
-        <v>16.514</v>
+        <v>16.47826</v>
       </c>
       <c r="F8" t="n">
-        <v>21.82031</v>
+        <v>21.90948</v>
       </c>
       <c r="G8" t="n">
-        <v>34.51513</v>
+        <v>34.18187</v>
       </c>
     </row>
   </sheetData>
